--- a/AAII_Financials/Yearly/BNL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BNL_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>BNL</t>
   </si>
@@ -656,172 +656,184 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>442900</v>
+      </c>
+      <c r="E8" s="3">
         <v>407500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>382900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>321600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>298800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>237500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>181600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>142900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>98100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E9" s="3">
         <v>61900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>51100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>56200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>41000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>29100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7700</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>385800</v>
+      </c>
+      <c r="E10" s="3">
         <v>345700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>331800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>265400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>257800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>208400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>163200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>130600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>90400</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,8 +848,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -871,9 +884,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,81 +923,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E14" s="3">
         <v>6200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>29900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>19500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>8700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>124100</v>
+      </c>
+      <c r="E15" s="3">
         <v>114700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>99200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>93800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>83800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>66100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>50400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>38000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>25000</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -993,80 +1018,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>251900</v>
+      </c>
+      <c r="E17" s="3">
         <v>219800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>215500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>201400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>165000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>128200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>101800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>79400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>54500</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E18" s="3">
         <v>187700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>167400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>120300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>133800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>109300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>79700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>63500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>43600</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,173 +1113,186 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E20" s="3">
         <v>21700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>13100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>26300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>19500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>14600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>396900</v>
+      </c>
+      <c r="E21" s="3">
         <v>359400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>304200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>264900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>265500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>212500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>157100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>116100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>72300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>80100</v>
+      </c>
+      <c r="E22" s="3">
         <v>78700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>64100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>76100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>72500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>52900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>34800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>30000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>22600</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>164100</v>
+      </c>
+      <c r="E23" s="3">
         <v>130800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>111200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>57200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>87500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>76000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>59600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>40300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20900</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1260,9 +1305,12 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1296,81 +1344,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>163300</v>
+      </c>
+      <c r="E26" s="3">
         <v>129500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>109500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>56300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>85100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>75100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>59600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>40300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>20900</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>154900</v>
+      </c>
+      <c r="E27" s="3">
         <v>121700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>102000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>51100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>79400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>69400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>54800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>36400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19300</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1404,9 +1461,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1440,9 +1500,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1476,9 +1539,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1512,81 +1578,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-53100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-21700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-13100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-26300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-19500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-14600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>154900</v>
+      </c>
+      <c r="E33" s="3">
         <v>121700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>102000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>51100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>79400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>69400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>54800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>36400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19300</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1620,86 +1695,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>154900</v>
+      </c>
+      <c r="E35" s="3">
         <v>121700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>102000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>51100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>79400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>69400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>54800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>36400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19300</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1714,8 +1798,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1730,44 +1815,48 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E41" s="3">
         <v>21800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>100500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>21600</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1801,45 +1890,51 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>154200</v>
+      </c>
+      <c r="E43" s="3">
         <v>137000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>118200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>103700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>85500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>70300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>52900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>36900</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1873,35 +1968,38 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E45" s="3">
         <v>8200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>19200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>300</v>
       </c>
       <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
+      <c r="K45" s="3">
+        <v>300</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
@@ -1909,9 +2007,12 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1945,9 +2046,12 @@
       <c r="M46" s="3">
         <v>0</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3">
+        <v>0</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1966,14 +2070,14 @@
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="3">
-        <v>16500</v>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J47" s="3">
         <v>16500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
+      <c r="K47" s="3">
+        <v>16500</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
@@ -1981,81 +2085,90 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4392800</v>
+      </c>
+      <c r="E48" s="3">
         <v>4505100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3807500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3387200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3458900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2683700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2227800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1685000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>639700</v>
+      </c>
+      <c r="E49" s="3">
         <v>677900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>653100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>641400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>344700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>300000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>256200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>179400</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2089,9 +2202,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2125,45 +2241,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E52" s="3">
         <v>44300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1900</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2197,45 +2319,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5268700</v>
+      </c>
+      <c r="E54" s="3">
         <v>5457600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4618600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4258500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3917900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3096800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2578800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1952100</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2250,8 +2378,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2266,44 +2395,48 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E57" s="3">
         <v>44800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>35500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>72300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>36200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>20300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17400</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2337,45 +2470,51 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E59" s="3">
         <v>64300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>55000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2409,45 +2548,51 @@
       <c r="M60" s="3">
         <v>0</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1910800</v>
+      </c>
+      <c r="E61" s="3">
         <v>2023200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1689300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1541200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1981200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1445800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1177700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>866600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2481,9 +2626,12 @@
       <c r="M62" s="3">
         <v>0</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2517,9 +2665,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2553,9 +2704,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2589,45 +2743,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2219500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2364700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2041400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1959400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2250200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1679700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1391900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1040300</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2642,8 +2802,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2677,9 +2838,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2713,9 +2877,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2749,9 +2916,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2785,45 +2955,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-440700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-386000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-318500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-259700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-208300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-155200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-120300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-90000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2857,9 +3033,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2893,9 +3072,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2929,45 +3111,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3049200</v>
+      </c>
+      <c r="E76" s="3">
         <v>3092900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2577300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2299100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1667600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1417100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1186800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>911800</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3001,86 +3189,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>154900</v>
+      </c>
+      <c r="E81" s="3">
         <v>121700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>102000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>51100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>79400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>69400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>54800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>36400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19300</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3095,44 +3292,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>152800</v>
+      </c>
+      <c r="E83" s="3">
         <v>150000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>128900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>131600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>105400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>83700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>62800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>45800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>28800</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3166,9 +3367,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3202,9 +3406,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3238,9 +3445,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3274,9 +3484,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3310,45 +3523,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>271100</v>
+      </c>
+      <c r="E89" s="3">
         <v>255900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>244900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>179000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>147400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>128000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>97900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>67200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>38600</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3363,44 +3582,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-170700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-916100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-666600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-106200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1002100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-581200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-675000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-502500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-502400</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3434,9 +3657,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3470,45 +3696,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-859600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-582300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-60200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-831700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-510500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-611100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-472000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-480500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3523,23 +3755,24 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-207500</v>
+      </c>
+      <c r="E96" s="3">
         <v>-181200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-154500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-71500</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -3558,9 +3791,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3594,9 +3830,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3630,9 +3869,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3666,45 +3908,51 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-334800</v>
+      </c>
+      <c r="E100" s="3">
         <v>636000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>254400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-28400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>685700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>391300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>500900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>399400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>464800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3738,43 +3986,49 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E102" s="3">
         <v>32300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-83000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>90400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>22900</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BNL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BNL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
   <si>
     <t>BNL</t>
   </si>
@@ -760,25 +760,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>57100</v>
+        <v>22600</v>
       </c>
       <c r="E9" s="3">
-        <v>61900</v>
+        <v>21800</v>
       </c>
       <c r="F9" s="3">
-        <v>51100</v>
+        <v>18500</v>
       </c>
       <c r="G9" s="3">
-        <v>56200</v>
+        <v>21200</v>
       </c>
       <c r="H9" s="3">
-        <v>41000</v>
+        <v>46100</v>
       </c>
       <c r="I9" s="3">
-        <v>29100</v>
+        <v>35900</v>
       </c>
       <c r="J9" s="3">
-        <v>18400</v>
+        <v>26200</v>
       </c>
       <c r="K9" s="3">
         <v>12200</v>
@@ -799,25 +799,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>385800</v>
+        <v>420300</v>
       </c>
       <c r="E10" s="3">
-        <v>345700</v>
+        <v>385700</v>
       </c>
       <c r="F10" s="3">
-        <v>331800</v>
+        <v>364400</v>
       </c>
       <c r="G10" s="3">
-        <v>265400</v>
+        <v>300400</v>
       </c>
       <c r="H10" s="3">
-        <v>257800</v>
+        <v>252700</v>
       </c>
       <c r="I10" s="3">
-        <v>208400</v>
+        <v>201600</v>
       </c>
       <c r="J10" s="3">
-        <v>163200</v>
+        <v>155300</v>
       </c>
       <c r="K10" s="3">
         <v>130600</v>
@@ -933,25 +933,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>32900</v>
+        <v>-22100</v>
       </c>
       <c r="E14" s="3">
-        <v>6200</v>
+        <v>-1600</v>
       </c>
       <c r="F14" s="3">
-        <v>29900</v>
+        <v>24400</v>
       </c>
       <c r="G14" s="3">
-        <v>19500</v>
+        <v>20900</v>
       </c>
       <c r="H14" s="3">
-        <v>4600</v>
+        <v>-21600</v>
       </c>
       <c r="I14" s="3">
-        <v>2200</v>
+        <v>-16800</v>
       </c>
       <c r="J14" s="3">
-        <v>7800</v>
+        <v>-5200</v>
       </c>
       <c r="K14" s="3">
         <v>11000</v>
@@ -972,25 +972,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>124100</v>
+        <v>157700</v>
       </c>
       <c r="E15" s="3">
-        <v>114700</v>
+        <v>146300</v>
       </c>
       <c r="F15" s="3">
-        <v>99200</v>
+        <v>128300</v>
       </c>
       <c r="G15" s="3">
-        <v>93800</v>
+        <v>118200</v>
       </c>
       <c r="H15" s="3">
-        <v>83800</v>
+        <v>108800</v>
       </c>
       <c r="I15" s="3">
-        <v>66100</v>
+        <v>84000</v>
       </c>
       <c r="J15" s="3">
-        <v>50400</v>
+        <v>62300</v>
       </c>
       <c r="K15" s="3">
         <v>38000</v>
@@ -1025,25 +1025,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>251900</v>
+        <v>219700</v>
       </c>
       <c r="E17" s="3">
-        <v>219800</v>
+        <v>205500</v>
       </c>
       <c r="F17" s="3">
-        <v>215500</v>
+        <v>183100</v>
       </c>
       <c r="G17" s="3">
-        <v>201400</v>
+        <v>167400</v>
       </c>
       <c r="H17" s="3">
-        <v>165000</v>
+        <v>160400</v>
       </c>
       <c r="I17" s="3">
-        <v>128200</v>
+        <v>126000</v>
       </c>
       <c r="J17" s="3">
-        <v>101800</v>
+        <v>93400</v>
       </c>
       <c r="K17" s="3">
         <v>79400</v>
@@ -1064,25 +1064,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>191000</v>
+        <v>223200</v>
       </c>
       <c r="E18" s="3">
-        <v>187700</v>
+        <v>202100</v>
       </c>
       <c r="F18" s="3">
-        <v>167400</v>
+        <v>199800</v>
       </c>
       <c r="G18" s="3">
-        <v>120300</v>
+        <v>154300</v>
       </c>
       <c r="H18" s="3">
-        <v>133800</v>
+        <v>138400</v>
       </c>
       <c r="I18" s="3">
-        <v>109300</v>
+        <v>111500</v>
       </c>
       <c r="J18" s="3">
-        <v>79700</v>
+        <v>88100</v>
       </c>
       <c r="K18" s="3">
         <v>63500</v>
@@ -1120,25 +1120,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>53100</v>
+        <v>1700</v>
       </c>
       <c r="E20" s="3">
-        <v>21700</v>
+        <v>-5700</v>
       </c>
       <c r="F20" s="3">
-        <v>7900</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>13100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>26300</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>19500</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>14600</v>
+        <v>-400</v>
       </c>
       <c r="K20" s="3">
         <v>6700</v>
@@ -1159,25 +1159,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>396900</v>
+        <v>379200</v>
       </c>
       <c r="E21" s="3">
-        <v>359400</v>
+        <v>354100</v>
       </c>
       <c r="F21" s="3">
-        <v>304200</v>
+        <v>328000</v>
       </c>
       <c r="G21" s="3">
-        <v>264900</v>
+        <v>272400</v>
       </c>
       <c r="H21" s="3">
-        <v>265500</v>
+        <v>247200</v>
       </c>
       <c r="I21" s="3">
-        <v>212500</v>
+        <v>195400</v>
       </c>
       <c r="J21" s="3">
-        <v>157100</v>
+        <v>150800</v>
       </c>
       <c r="K21" s="3">
         <v>116100</v>
@@ -1255,7 +1255,7 @@
         <v>76000</v>
       </c>
       <c r="J23" s="3">
-        <v>59600</v>
+        <v>60200</v>
       </c>
       <c r="K23" s="3">
         <v>40300</v>
@@ -1293,8 +1293,8 @@
       <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>600</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1402,7 +1402,7 @@
         <v>102000</v>
       </c>
       <c r="G27" s="3">
-        <v>51100</v>
+        <v>51000</v>
       </c>
       <c r="H27" s="3">
         <v>79400</v>
@@ -1588,25 +1588,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-53100</v>
+        <v>-1700</v>
       </c>
       <c r="E32" s="3">
-        <v>-21700</v>
+        <v>5700</v>
       </c>
       <c r="F32" s="3">
-        <v>-7900</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>-13100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-26300</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-19500</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>-14600</v>
+        <v>400</v>
       </c>
       <c r="K32" s="3">
         <v>-6700</v>
@@ -1627,16 +1627,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>154900</v>
+        <v>155500</v>
       </c>
       <c r="E33" s="3">
-        <v>121700</v>
+        <v>122100</v>
       </c>
       <c r="F33" s="3">
-        <v>102000</v>
+        <v>102400</v>
       </c>
       <c r="G33" s="3">
-        <v>51100</v>
+        <v>51200</v>
       </c>
       <c r="H33" s="3">
         <v>79400</v>
@@ -1705,16 +1705,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>154900</v>
+        <v>155500</v>
       </c>
       <c r="E35" s="3">
-        <v>121700</v>
+        <v>122100</v>
       </c>
       <c r="F35" s="3">
-        <v>102000</v>
+        <v>102400</v>
       </c>
       <c r="G35" s="3">
-        <v>51100</v>
+        <v>51200</v>
       </c>
       <c r="H35" s="3">
         <v>79400</v>
@@ -1861,10 +1861,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>46100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>63400</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -1873,13 +1873,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>17600</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -1900,25 +1900,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>154200</v>
+        <v>181400</v>
       </c>
       <c r="E43" s="3">
-        <v>137000</v>
+        <v>164600</v>
       </c>
       <c r="F43" s="3">
-        <v>118200</v>
+        <v>147500</v>
       </c>
       <c r="G43" s="3">
-        <v>103700</v>
+        <v>133400</v>
       </c>
       <c r="H43" s="3">
-        <v>85500</v>
+        <v>127400</v>
       </c>
       <c r="I43" s="3">
-        <v>70300</v>
+        <v>112300</v>
       </c>
       <c r="J43" s="3">
-        <v>52900</v>
+        <v>101100</v>
       </c>
       <c r="K43" s="3">
         <v>36900</v>
@@ -1938,26 +1938,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>15400</v>
+        <v>27000</v>
       </c>
       <c r="E45" s="3">
         <v>8200</v>
@@ -1987,16 +1987,16 @@
         <v>8100</v>
       </c>
       <c r="G45" s="3">
-        <v>19200</v>
+        <v>9000</v>
       </c>
       <c r="H45" s="3">
-        <v>11000</v>
+        <v>2500</v>
       </c>
       <c r="I45" s="3">
-        <v>2800</v>
+        <v>3900</v>
       </c>
       <c r="J45" s="3">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="K45" s="3">
         <v>300</v>
@@ -2017,25 +2017,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>275200</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>296300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>183400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>253000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>153100</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>152800</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>123400</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2074,7 +2074,7 @@
         <v>3</v>
       </c>
       <c r="J47" s="3">
-        <v>16500</v>
+        <v>10000</v>
       </c>
       <c r="K47" s="3">
         <v>16500</v>
@@ -2095,25 +2095,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4392800</v>
+        <v>4270600</v>
       </c>
       <c r="E48" s="3">
-        <v>4505100</v>
+        <v>4477500</v>
       </c>
       <c r="F48" s="3">
-        <v>3807500</v>
+        <v>3778100</v>
       </c>
       <c r="G48" s="3">
-        <v>3387200</v>
+        <v>3357600</v>
       </c>
       <c r="H48" s="3">
-        <v>3458900</v>
+        <v>3417000</v>
       </c>
       <c r="I48" s="3">
-        <v>2683700</v>
+        <v>2641700</v>
       </c>
       <c r="J48" s="3">
-        <v>2227800</v>
+        <v>2186100</v>
       </c>
       <c r="K48" s="3">
         <v>1685000</v>
@@ -2134,25 +2134,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>639700</v>
+        <v>628000</v>
       </c>
       <c r="E49" s="3">
-        <v>677900</v>
+        <v>669400</v>
       </c>
       <c r="F49" s="3">
-        <v>653100</v>
+        <v>643400</v>
       </c>
       <c r="G49" s="3">
-        <v>641400</v>
+        <v>630700</v>
       </c>
       <c r="H49" s="3">
-        <v>344700</v>
+        <v>331900</v>
       </c>
       <c r="I49" s="3">
-        <v>300000</v>
+        <v>286300</v>
       </c>
       <c r="J49" s="3">
-        <v>256200</v>
+        <v>242700</v>
       </c>
       <c r="K49" s="3">
         <v>179400</v>
@@ -2251,25 +2251,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>44300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>10200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>2400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>3800</v>
+        <v>95000</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>1900</v>
@@ -2402,25 +2402,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>39300</v>
+        <v>24500</v>
       </c>
       <c r="E57" s="3">
-        <v>44800</v>
+        <v>26000</v>
       </c>
       <c r="F57" s="3">
-        <v>35500</v>
+        <v>20300</v>
       </c>
       <c r="G57" s="3">
-        <v>72300</v>
+        <v>17200</v>
       </c>
       <c r="H57" s="3">
-        <v>36200</v>
+        <v>18300</v>
       </c>
       <c r="I57" s="3">
-        <v>22300</v>
+        <v>13300</v>
       </c>
       <c r="J57" s="3">
-        <v>20300</v>
+        <v>11800</v>
       </c>
       <c r="K57" s="3">
         <v>17400</v>
@@ -2441,19 +2441,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2480,25 +2480,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>70800</v>
+        <v>71600</v>
       </c>
       <c r="E59" s="3">
-        <v>64300</v>
+        <v>73200</v>
       </c>
       <c r="F59" s="3">
-        <v>55000</v>
+        <v>61100</v>
       </c>
       <c r="G59" s="3">
-        <v>6700</v>
+        <v>55100</v>
       </c>
       <c r="H59" s="3">
-        <v>4800</v>
+        <v>17900</v>
       </c>
       <c r="I59" s="3">
-        <v>9900</v>
+        <v>11100</v>
       </c>
       <c r="J59" s="3">
-        <v>4000</v>
+        <v>14300</v>
       </c>
       <c r="K59" s="3">
         <v>2000</v>
@@ -2519,25 +2519,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>104100</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>106300</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>147900</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>76500</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>39900</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>34300</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>30100</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2558,25 +2558,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1910800</v>
+        <v>1916800</v>
       </c>
       <c r="E61" s="3">
-        <v>2023200</v>
+        <v>2025900</v>
       </c>
       <c r="F61" s="3">
-        <v>1689300</v>
+        <v>1659000</v>
       </c>
       <c r="G61" s="3">
-        <v>1541200</v>
+        <v>1615700</v>
       </c>
       <c r="H61" s="3">
-        <v>1981200</v>
+        <v>2006800</v>
       </c>
       <c r="I61" s="3">
-        <v>1445800</v>
+        <v>1447600</v>
       </c>
       <c r="J61" s="3">
-        <v>1177700</v>
+        <v>1182800</v>
       </c>
       <c r="K61" s="3">
         <v>866600</v>
@@ -2597,25 +2597,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>53500</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>62900</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>70600</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>87200</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>92200</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>85900</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>81700</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -2753,25 +2753,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2219500</v>
+        <v>2074400</v>
       </c>
       <c r="E66" s="3">
-        <v>2364700</v>
+        <v>2195100</v>
       </c>
       <c r="F66" s="3">
-        <v>2041400</v>
+        <v>1877500</v>
       </c>
       <c r="G66" s="3">
-        <v>1959400</v>
+        <v>1779400</v>
       </c>
       <c r="H66" s="3">
-        <v>2250200</v>
+        <v>2138800</v>
       </c>
       <c r="I66" s="3">
-        <v>1679700</v>
+        <v>1567900</v>
       </c>
       <c r="J66" s="3">
-        <v>1391900</v>
+        <v>1294600</v>
       </c>
       <c r="K66" s="3">
         <v>1040300</v>
@@ -2964,26 +2964,26 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-440700</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-386000</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-318500</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-259700</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-208300</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-155200</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-120300</v>
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3">
         <v>-90000</v>
@@ -3243,16 +3243,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>154900</v>
+        <v>155500</v>
       </c>
       <c r="E81" s="3">
-        <v>121700</v>
+        <v>122100</v>
       </c>
       <c r="F81" s="3">
-        <v>102000</v>
+        <v>102400</v>
       </c>
       <c r="G81" s="3">
-        <v>51100</v>
+        <v>51200</v>
       </c>
       <c r="H81" s="3">
         <v>79400</v>
@@ -3299,25 +3299,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>152800</v>
+        <v>124200</v>
       </c>
       <c r="E83" s="3">
-        <v>150000</v>
+        <v>114700</v>
       </c>
       <c r="F83" s="3">
-        <v>128900</v>
+        <v>99300</v>
       </c>
       <c r="G83" s="3">
-        <v>131600</v>
+        <v>93800</v>
       </c>
       <c r="H83" s="3">
-        <v>105400</v>
+        <v>83800</v>
       </c>
       <c r="I83" s="3">
-        <v>83700</v>
+        <v>66100</v>
       </c>
       <c r="J83" s="3">
-        <v>62800</v>
+        <v>50400</v>
       </c>
       <c r="K83" s="3">
         <v>45800</v>
@@ -3589,25 +3589,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-170700</v>
+        <v>-46300</v>
       </c>
       <c r="E91" s="3">
-        <v>-916100</v>
+        <v>-31400</v>
       </c>
       <c r="F91" s="3">
-        <v>-666600</v>
+        <v>-1600</v>
       </c>
       <c r="G91" s="3">
-        <v>-106200</v>
+        <v>-10800</v>
       </c>
       <c r="H91" s="3">
-        <v>-1002100</v>
+        <v>-5100</v>
       </c>
       <c r="I91" s="3">
-        <v>-581200</v>
+        <v>-5200</v>
       </c>
       <c r="J91" s="3">
-        <v>-675000</v>
+        <v>-6800</v>
       </c>
       <c r="K91" s="3">
         <v>-502500</v>
@@ -3724,7 +3724,7 @@
         <v>-510500</v>
       </c>
       <c r="J94" s="3">
-        <v>-611100</v>
+        <v>-611800</v>
       </c>
       <c r="K94" s="3">
         <v>-472000</v>
@@ -3762,25 +3762,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-207500</v>
+        <v>207500</v>
       </c>
       <c r="E96" s="3">
-        <v>-181200</v>
+        <v>181200</v>
       </c>
       <c r="F96" s="3">
-        <v>-154500</v>
+        <v>154500</v>
       </c>
       <c r="G96" s="3">
-        <v>-71500</v>
+        <v>71500</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>51800</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>44500</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3956,26 +3956,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4014,7 +4014,7 @@
         <v>8900</v>
       </c>
       <c r="J102" s="3">
-        <v>-12300</v>
+        <v>-13000</v>
       </c>
       <c r="K102" s="3">
         <v>-5400</v>

--- a/AAII_Financials/Yearly/BNL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BNL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
   <si>
     <t>BNL</t>
   </si>
@@ -656,184 +656,196 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>431800</v>
+      </c>
+      <c r="E8" s="3">
         <v>442900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>407500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>382900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>321600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>298800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>237500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>181600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>142900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>98100</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E9" s="3">
         <v>22600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>21800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>21200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>46100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>35900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7700</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>407100</v>
+      </c>
+      <c r="E10" s="3">
         <v>420300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>385700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>364400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>300400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>252700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>201600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>155300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>130600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>90400</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,8 +861,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -887,9 +900,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,87 +942,96 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-22100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>24400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>20900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-21600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-16800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-5200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>8700</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>154600</v>
+      </c>
+      <c r="E15" s="3">
         <v>157700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>146300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>128300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>118200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>108800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>84000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>62300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>38000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>25000</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1019,86 +1044,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>216900</v>
+      </c>
+      <c r="E17" s="3">
         <v>219700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>205500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>183100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>167400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>160400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>126000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>93400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>79400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>54500</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>214900</v>
+      </c>
+      <c r="E18" s="3">
         <v>223200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>202100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>199800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>154300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>138400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>111500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>88100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>63500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>43600</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1114,191 +1146,204 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E20" s="3">
         <v>1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>375700</v>
+      </c>
+      <c r="E21" s="3">
         <v>379200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>354100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>328000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>272400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>247200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>195400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>150800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>116100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>72300</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E22" s="3">
         <v>80100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>78700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>64100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>76100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>72500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>52900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>34800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>30000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>22600</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>170200</v>
+      </c>
+      <c r="E23" s="3">
         <v>164100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>130800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>111200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>57200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>87500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>76000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>60200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>40300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>20900</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1308,9 +1353,12 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1347,87 +1395,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E26" s="3">
         <v>163300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>129500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>109500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>56300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>85100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>75100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>59600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>40300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>20900</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>161300</v>
+      </c>
+      <c r="E27" s="3">
         <v>154900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>121700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>102000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>51000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>79400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>69400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>54800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>36400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19300</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1464,9 +1521,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1503,9 +1563,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1542,9 +1605,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1581,87 +1647,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>162400</v>
+      </c>
+      <c r="E33" s="3">
         <v>155500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>122100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>102400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>51200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>79400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>69400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>54800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>36400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19300</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1698,92 +1773,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>162400</v>
+      </c>
+      <c r="E35" s="3">
         <v>155500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>122100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>102400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>51200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>79400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>69400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>54800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>36400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19300</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1799,8 +1883,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1816,74 +1901,78 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E41" s="3">
         <v>19500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>100500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21600</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E42" s="3">
         <v>46100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>63400</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>2900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -1893,48 +1982,54 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>192700</v>
+      </c>
+      <c r="E43" s="3">
         <v>181400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>164600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>147500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>133400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>127400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>112300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>101100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>36900</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1959,8 +2054,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1971,75 +2066,81 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>27000</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>8200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>275200</v>
+        <v>254900</v>
       </c>
       <c r="E46" s="3">
+        <v>248200</v>
+      </c>
+      <c r="F46" s="3">
         <v>296300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>183400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>253000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>153100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>152800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>123400</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2049,9 +2150,12 @@
       <c r="N46" s="3">
         <v>0</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2073,102 +2177,111 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>10000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>16500</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4305100</v>
+      </c>
+      <c r="E48" s="3">
         <v>4270600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4477500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3778100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3357600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3417000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2641700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2186100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1685000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>607400</v>
+      </c>
+      <c r="E49" s="3">
         <v>628000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>669400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>643400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>630700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>331900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>286300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>242700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>179400</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2205,9 +2318,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2244,17 +2360,20 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>95000</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+        <v>49000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>122000</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -2271,21 +2390,24 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
         <v>1900</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2322,48 +2444,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5216400</v>
+      </c>
+      <c r="E54" s="3">
         <v>5268700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5457600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4618600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4258500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3917900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3096800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2578800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1952100</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2379,8 +2507,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2396,68 +2525,72 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E57" s="3">
         <v>24500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>26000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>18300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17400</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2300</v>
+        <v>18300</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>60000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>100</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -2473,75 +2606,81 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E59" s="3">
         <v>71600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>73200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>61100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>55100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2000</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>104100</v>
+        <v>121200</v>
       </c>
       <c r="E60" s="3">
+        <v>101800</v>
+      </c>
+      <c r="F60" s="3">
         <v>106300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>147900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>76500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>39900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30100</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2551,75 +2690,81 @@
       <c r="N60" s="3">
         <v>0</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1916800</v>
+        <v>1905000</v>
       </c>
       <c r="E61" s="3">
+        <v>1919000</v>
+      </c>
+      <c r="F61" s="3">
         <v>2025900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1659000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1615700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2006800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1447600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1182800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>866600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E62" s="3">
         <v>53500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>62900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>70600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>87200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>92200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>85900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>81700</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -2629,9 +2774,12 @@
       <c r="N62" s="3">
         <v>0</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2668,9 +2816,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2707,9 +2858,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2746,48 +2900,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2075000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2074400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2195100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1877500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1779400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2138800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1567900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1294600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1040300</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2803,8 +2963,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2841,9 +3002,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2880,9 +3044,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2919,9 +3086,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2958,9 +3128,12 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2985,21 +3158,24 @@
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3">
         <v>-90000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3036,9 +3212,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3075,9 +3254,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3114,48 +3296,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3003700</v>
+      </c>
+      <c r="E76" s="3">
         <v>3049200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3092900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2577300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2299100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1667600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1417100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1186800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>911800</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3192,92 +3380,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>162400</v>
+      </c>
+      <c r="E81" s="3">
         <v>155500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>122100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>102400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>51200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>79400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>69400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>54800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>36400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19300</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3293,47 +3490,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E83" s="3">
         <v>124200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>114700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>99300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>93800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>83800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>66100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>50400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>45800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>28800</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3370,9 +3571,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3409,9 +3613,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3448,9 +3655,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3487,9 +3697,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3526,48 +3739,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>276300</v>
+      </c>
+      <c r="E89" s="3">
         <v>271100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>255900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>244900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>179000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>147400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>128000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>97900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>67200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>38600</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3583,47 +3802,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-46300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-31400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-502500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-502400</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3660,9 +3883,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3699,48 +3925,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-59700</v>
+      </c>
+      <c r="E94" s="3">
         <v>24300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-859600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-582300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-60200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-831700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-510500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-611800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-472000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-480500</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3756,35 +3988,36 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>216800</v>
+      </c>
+      <c r="E96" s="3">
         <v>207500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>181200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>154500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>71500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>62000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>51800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>44500</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -3794,9 +4027,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3833,9 +4069,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3872,9 +4111,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3911,48 +4153,54 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-221200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-334800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>636000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>254400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-28400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>685700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>391300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>500900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>399400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>464800</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3977,8 +4225,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3989,46 +4237,52 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-39400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>32300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-83000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>90400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>22900</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BNL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BNL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
   <si>
     <t>BNL</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>454100</v>
+      </c>
+      <c r="E8" s="3">
         <v>431800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>442900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>407500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>382900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>321600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>298800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>237500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>181600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>142900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>98100</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E9" s="3">
         <v>24700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>22600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>21800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>21200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>46100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>35900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>26200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7700</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>431200</v>
+      </c>
+      <c r="E10" s="3">
         <v>407100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>420300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>385700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>364400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>300400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>252700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>201600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>155300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>130600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>90400</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,93 +961,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-22200</v>
+        <v>32400</v>
       </c>
       <c r="E14" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="F14" s="3">
         <v>-22100</v>
       </c>
-      <c r="F14" s="3">
-        <v>-1600</v>
-      </c>
       <c r="G14" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="H14" s="3">
         <v>24400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>20900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-21600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-16800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-5200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>158800</v>
+      </c>
+      <c r="E15" s="3">
         <v>154600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>157700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>146300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>128300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>118200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>108800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>84000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>62300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>38000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>25000</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>216900</v>
+        <v>220600</v>
       </c>
       <c r="E17" s="3">
+        <v>217300</v>
+      </c>
+      <c r="F17" s="3">
         <v>219700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>205500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>183100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>167400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>160400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>126000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>93400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>79400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>54500</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>214900</v>
+        <v>233500</v>
       </c>
       <c r="E18" s="3">
+        <v>214500</v>
+      </c>
+      <c r="F18" s="3">
         <v>223200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>202100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>199800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>154300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>138400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>111500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>88100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>63500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>43600</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,176 +1179,189 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
-        <v>-5700</v>
-      </c>
       <c r="G20" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>375700</v>
+        <v>385900</v>
       </c>
       <c r="E21" s="3">
+        <v>375300</v>
+      </c>
+      <c r="F21" s="3">
         <v>379200</v>
       </c>
-      <c r="F21" s="3">
-        <v>354100</v>
-      </c>
       <c r="G21" s="3">
+        <v>353700</v>
+      </c>
+      <c r="H21" s="3">
         <v>328000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>272400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>247200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>195400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>150800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>116100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>72300</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>94500</v>
+      </c>
+      <c r="E22" s="3">
         <v>74100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>80100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>78700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>64100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>76100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>72500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>52900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>34800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>30000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>22600</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>100600</v>
+      </c>
+      <c r="E23" s="3">
         <v>170200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>164100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>130800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>111200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>57200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>87500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>76000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>60200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>40300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>20900</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1324,29 +1369,29 @@
         <v>1200</v>
       </c>
       <c r="E24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1356,9 +1401,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>99400</v>
+      </c>
+      <c r="E26" s="3">
         <v>169000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>163300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>129500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>109500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>56300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>85100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>75100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>59600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>40300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20900</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E27" s="3">
         <v>161300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>154900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>121700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>102000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>51000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>79400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>69400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>54800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>36400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19300</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E32" s="3">
         <v>6200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
-        <v>5700</v>
-      </c>
       <c r="G32" s="3">
+        <v>5400</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>96500</v>
+      </c>
+      <c r="E33" s="3">
         <v>162400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>155500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>122100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>102400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>51200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>79400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>69400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>54800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>36400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19300</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>96500</v>
+      </c>
+      <c r="E35" s="3">
         <v>162400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>155500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>122100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>102400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>51200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>79400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>69400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>54800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>36400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19300</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,80 +1987,84 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E41" s="3">
         <v>14800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>100500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21600</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E42" s="3">
         <v>46200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>46100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>63400</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>2900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>17600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -1985,51 +2074,57 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>223200</v>
+      </c>
+      <c r="E43" s="3">
         <v>192700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>181400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>164600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>147500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>133400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>127400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>112300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>101100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>36900</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2057,8 +2152,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2069,81 +2164,87 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>30200</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>8200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>254900</v>
+        <v>316100</v>
       </c>
       <c r="E46" s="3">
+        <v>285100</v>
+      </c>
+      <c r="F46" s="3">
         <v>248200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>296300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>183400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>253000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>153100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>152800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>123400</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2153,9 +2254,12 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2180,108 +2284,117 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>10000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>16500</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4527600</v>
+      </c>
+      <c r="E48" s="3">
         <v>4305100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4270600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4477500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3778100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3357600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3417000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2641700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2186100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1685000</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>607800</v>
+      </c>
+      <c r="E49" s="3">
         <v>607400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>628000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>669400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>643400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>630700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>331900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>286300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>242700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>179400</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,21 +2479,24 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>49000</v>
+        <v>265800</v>
       </c>
       <c r="E52" s="3">
+        <v>18800</v>
+      </c>
+      <c r="F52" s="3">
         <v>122000</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2393,21 +2512,24 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3">
         <v>1900</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5717300</v>
+      </c>
+      <c r="E54" s="3">
         <v>5216400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5268700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5457600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4618600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4258500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3917900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3096800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2578800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1952100</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,74 +2655,78 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E57" s="3">
         <v>22200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>26000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17400</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E58" s="3">
         <v>18300</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>60000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>100</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -2609,81 +2742,87 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E59" s="3">
         <v>74900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>71600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>73200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>61100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>55100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2000</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>137600</v>
+      </c>
+      <c r="E60" s="3">
         <v>121200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>101800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>106300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>147900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>76500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>39900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30100</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2693,81 +2832,87 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2504600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1905000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1919000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2025900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1659000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1615700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2006800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1447600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1182800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>866600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>41500</v>
+      </c>
+      <c r="E62" s="3">
         <v>48700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>53500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>62900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>70600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>87200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>92200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>85900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>81700</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2683800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2075000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2074400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2195100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1877500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1779400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2138800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1567900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1294600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1040300</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,9 +3301,12 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3161,21 +3334,24 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3">
         <v>-90000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2902000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3003700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3049200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3092900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2577300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2299100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1667600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1417100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1186800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>911800</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>96500</v>
+      </c>
+      <c r="E81" s="3">
         <v>162400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>155500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>122100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>102400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>51200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>79400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>69400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>54800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>36400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19300</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>129100</v>
+      </c>
+      <c r="E83" s="3">
         <v>124000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>124200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>114700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>99300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>93800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>83800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>66100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>50400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>45800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>28800</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>299500</v>
+      </c>
+      <c r="E89" s="3">
         <v>276300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>271100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>255900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>244900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>179000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>147400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>128000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>97900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>67200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>38600</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-502500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-502400</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-675300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-59700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>24300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-859600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-582300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-60200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-831700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-510500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-611800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-472000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-480500</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,38 +4221,39 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>218800</v>
+      </c>
+      <c r="E96" s="3">
         <v>216800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>207500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>181200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>154500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>71500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>62000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>51800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>44500</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,51 +4398,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>393400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-221200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-334800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>636000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>254400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-28400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>685700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>391300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>399400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>464800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4228,8 +4476,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4240,49 +4488,55 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-39400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>32300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-83000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>90400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>22900</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
